--- a/dados_site/membros.xlsx
+++ b/dados_site/membros.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="n"/>
@@ -586,7 +585,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Coordenador do GES</t>
+          <t>Coordenador</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -614,11 +613,7 @@
           <t>https://www.researchgate.net/profile/Enedir-Ghisi</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>enedir.ghisi@ufsc.br</t>
-        </is>
-      </c>
+      <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -664,7 +659,7 @@
           <t>https://www.researchgate.net/profile/Liseane-Thives</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -672,45 +667,45 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Taylana Piccinini Scolaro</t>
+          <t>Igor Catão Martins Vaz</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Pós-Doutoranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Pesquisadora Pós-Doc</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>taylanapscolaro.png</t>
+          <t>igorcmvaz.png</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>./assets/team/taylanapscolaro.png</t>
+          <t>./assets/team/igorcmvaz.png</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0003-4296-0686</t>
+          <t>https://orcid.org/0000-0003-2433-223X</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/7183244717269690</t>
+          <t>http://lattes.cnpq.br/3846201039408286</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Taylana-Scolaro</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
+          <t>https://www.researchgate.net/profile/Igor-Vaz-3</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -756,7 +751,7 @@
           <t>https://www.researchgate.net/profile/Aline-Schaefer</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -764,47 +759,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Igor Catão Martins Vaz</t>
+          <t>Joelia Silva Cavalcante</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pesquisador</t>
+          <t>Doutoranda</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Pesquisador Líder</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>igorcmvaz.png</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>./assets/team/igorcmvaz.png</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0003-2433-223X</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/3846201039408286</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Igor-Vaz-3</t>
-        </is>
-      </c>
+          <t>Doutoranda</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>igor.vaz@posgrad.ufsc.br</t>
+          <t>joeliacavalcante@gmail.com</t>
         </is>
       </c>
     </row>
@@ -814,45 +789,25 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Priscila Zampier</t>
+          <t>Dilson Machado Cunha</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Mestranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Pesquisadora Mestrado</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>priscila.jpeg</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>./assets/team/priscila.jpeg</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0001-5577-2441</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>https://lattes.cnpq.br/2233053067068322</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Priscila-Zampier-2?ev=hdr_xprf</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
+          <t>Doutorando</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -860,45 +815,25 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mirela Moreira Ribeiro</t>
+          <t>Marco Aurelio Vieira Boufleur</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/6997171456515468</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
+          <t>Doutorando</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -906,45 +841,45 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Deivis Luis Marinoski</t>
+          <t>Priscila Zampier</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>priscila.jpeg</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>./assets/team/priscila.jpeg</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://orcid.org/0009-0001-5577-2441</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/3425265765339888</t>
+          <t>https://lattes.cnpq.br/2233053067068322</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
+          <t>https://www.researchgate.net/profile/Priscila-Zampier-2?ev=hdr_xprf</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -952,45 +887,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Forgiarini Rupp</t>
+          <t>Amanda Costa Ramos</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/0355666000210770</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>amanda.costa.arqeurb@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -998,45 +917,25 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Arthur Santos Silva</t>
+          <t>Laryssa Bitencourt Anselmo</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/7017962493418481</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1044,45 +943,25 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Abel Silva Vieira</t>
+          <t>João Pedro Gemelli Reali</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestrando</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/6438763922605609</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
+          <t>Mestrando</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1090,45 +969,25 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Mateus Vinícius Bavaresco</t>
+          <t>Matheus Do Nascimento Martins</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestrando</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/1682595069602838</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
+          <t>Mestrando</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1136,45 +995,25 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Andrea Invidiata</t>
+          <t>Rita Carolina Aimi</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/0578767852356933</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1182,7 +1021,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Max Weeber</t>
+          <t>Mirela Moreira Ribeiro</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1192,35 +1031,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
+          <t>http://lattes.cnpq.br/6997171456515468</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1228,45 +1051,199 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Deivis Luis Marinoski</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/3425265765339888</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ricardo Forgiarini Rupp</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/0355666000210770</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arthur Santos Silva</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/7017962493418481</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Abel Silva Vieira</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6438763922605609</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mateus Vinícius Bavaresco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/1682595069602838</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Andrea Invidiata</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/0578767852356933</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Max Weeber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ex-Membro</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Rafael Almeida Flores</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ex-Membro</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Ex-Pesquisador</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>http://lattes.cnpq.br/3476347525352024</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_site/membros.xlsx
+++ b/dados_site/membros.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,510 +570,489 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Enedir Ghisi</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Docente</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Coordenador</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>enedirghisi.png</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>./assets/team/enedirghisi.png</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://orcid.org/0000-0001-5918-6397</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>http://lattes.cnpq.br/0067772895372542</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/profile/Enedir-Ghisi</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Liseane Padilha Thives</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Docente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Pesquisadora</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>liseanepthives.jpeg</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>./assets/team/liseanepthives.jpeg</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://orcid.org/0000-0002-4782-2496</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>http://lattes.cnpq.br/3913788588121411</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/profile/Liseane-Thives</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Igor Catão Martins Vaz</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>igorcmvaz.png</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>./assets/team/igorcmvaz.png</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://orcid.org/0000-0003-2433-223X</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>http://lattes.cnpq.br/3846201039408286</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/profile/Igor-Vaz-3</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Aline Schaefer</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Pós-Doutoranda</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Pesquisadora Pós-Doc</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>alineschaefer.png</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>./assets/team/alineschaefer.png</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://orcid.org/0000-0001-8870-9863</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>http://lattes.cnpq.br/8826147751184750</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/profile/Aline-Schaefer</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Joelia Silva Cavalcante</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Doutoranda</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Doutoranda</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>joeliacavalcante@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Dilson Machado Cunha</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Marco Aurelio Vieira Boufleur</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Doutorando</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Priscila Zampier</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>priscila.jpeg</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>./assets/team/priscila.jpeg</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://orcid.org/0009-0001-5577-2441</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://lattes.cnpq.br/2233053067068322</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/profile/Priscila-Zampier-2?ev=hdr_xprf</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Amanda Costa Ramos</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>amanda.costa.arqeurb@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Laryssa Bitencourt Anselmo</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>João Pedro Gemelli Reali</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Mestrando</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Mestrando</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Matheus Do Nascimento Martins</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Mestrando</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Mestrando</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>matheusmartins.JPG</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>./assets/team/matheusmartins.JPG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0007-5434-8693</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://lattes.cnpq.br/8801886077639414</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Matheus-Martins-57</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Rita Carolina Aimi</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Mestranda</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Mirela Moreira Ribeiro</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Ex-Membro</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/6997171456515468</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rafael Almeida Flores</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pós-Doutorando</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pesquisador Pós-Doc</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rafaelflores.jpeg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>./assets/team/rafaelflores.jpeg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-9374-1865</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://lattes.cnpq.br/3476347525352024</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Rafael-Flores-21?ev=prf_overview</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Deivis Luis Marinoski</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Ex-Membro</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/3425265765339888</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Andrea Teston</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ex-Membro Pós-Doc</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora Pós-Doc</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1081,22 +1060,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ricardo Forgiarini Rupp</t>
+          <t>Celimar Azambuja Teixeira</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/0355666000210770</t>
+          <t>http://lattes.cnpq.br/6702681725561460</t>
         </is>
       </c>
     </row>
@@ -1106,22 +1085,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arthur Santos Silva</t>
+          <t>Cláudia Donald Pereira</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/7017962493418481</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
         </is>
       </c>
     </row>
@@ -1131,22 +1105,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abel Silva Vieira</t>
+          <t>Ricardo Forgiarini Rupp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisador Pós-Doc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/6438763922605609</t>
+          <t>http://lattes.cnpq.br/0355666000210770</t>
         </is>
       </c>
     </row>
@@ -1156,22 +1130,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mateus Vinícius Bavaresco</t>
+          <t>Taylana Piccinini Scolaro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/1682595069602838</t>
+          <t>http://lattes.cnpq.br/7183244717269690</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1155,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Andrea Invidiata</t>
+          <t>Ana Kelly Marinoski Ribeiro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/0578767852356933</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1175,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Max Weeber</t>
+          <t>Andreza Kalbusch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1195,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rafael Almeida Flores</t>
+          <t>Arthur Santos Silva</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ex-Membro</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1241,7 +1210,3292 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/3476347525352024</t>
+          <t>http://lattes.cnpq.br/7017962493418481</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bruna Faitão Balvedi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bruna Just Meller</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Diego Antônio Custódio</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Igor Schnaider de Souza</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Isabel Kroeff Braz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lucas Niehuns Antunes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Luiz Solon Souza Barreto</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Marina Ribeiro Viana</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mateus Vinícius Bavaresco</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/1682595069602838</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Matheus Soares Geraldi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Talita Flores Dias</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tânia Mara Sebben Oneda</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Thayane Lodete Bilésimo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ulisses Munarim</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deivis Luis Marinoski</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/3425265765339888</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Andrea Invidiata</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ex-Membro Doutorado</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/0578767852356933</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Abel Silva Vieira</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6438763922605609</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aline Eloize Borgert</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Andrigo Demetrio da Silva</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ariadne Marques de Mendonça</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Augusto Martins Marques</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cláudia Morishita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Douglas Ancelmo Freitas</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Eduardo Pierozan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Eldenir Guedes Teodoro</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Epaminondas de Souza Lage</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fabrícia de Oliveira Grando</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Greici Ramos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gustavo Coutinho Rosa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Jéssica Kuntz Maykot</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Joana Anny Mafalda de Oliveira</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>José Francisco Campos Moreira</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Julia Beatriz Saugo Milani</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Juliana May Sangoi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>57</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kácia Henderson Barbosa</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Laiane Susan S. Almeida</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>59</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lais de Bortoli Klein</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Laura Michelle Leite Ribeiro</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Leticia Dalpaz de Azevedo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>62</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Luís Fernando Kidinho Araújo dos Santos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>63</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Marcelo Dalmédico Ioris</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>64</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Marina Vasconcelos Santana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>65</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Marlon Eduardo Rodrigues</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>66</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Mauricio Dias da Conceição Neto</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Roberta Jacoby Cureau</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>68</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rodrigo Novais Istchuk</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tiago Arent Longo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>70</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tiago Diehl de Souza</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>71</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Vinicius Luis Rocha</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>72</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Wagner Isidoro Simioni</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>73</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Max Weeber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ex-Membro Mestrado</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Acácio Gomes Corrêa Silvestre</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Alef Pereira</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Alexandre Maestri</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Amanda Geraldo Andrighi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>78</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ana Gabriela S A Cardoso</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>79</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ana Júlia Deffaci Deresz</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>80</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ana Júlia Heisler de Oliveira</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>81</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>André Castellani Lopes</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>82</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>André Neis Botelho</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>83</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Andreza Montibeller</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>84</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Anna Luiza Schiefler Wallner</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>85</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Anthony Midori Fugi</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>86</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Beatriz Bayestorff Muller</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>87</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bernardo Farias Asmus</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>88</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Bruno Ariosa de Souza</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>89</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Caio Morelli Figueroba</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>90</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Caio Wolf Klein</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>91</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Candi Citadini de Oliveira</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>92</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Carolina Cannella Peña</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>93</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cecília Soares Faco</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>94</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Daniel Fabricio Ferreira</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>95</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Dario Menegasso Pires</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>96</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Davi da Fonseca Tavares</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>97</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>David Junior Gonçalves da Silva</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>98</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Débora Casasola</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>99</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Diego Bressan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>100</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Douglas Gherardt Brecht</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>101</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Douglas Leandro Meincheim</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>102</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Douglas Vigarani Scalco</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>103</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Eduardo Bald</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>104</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Eduardo Leite Souza</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>105</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Eric Serafim Franco</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>106</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Felipe Cidade Soares</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>107</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Felipe Martini</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>108</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Felipe Scotti Alves Tonin Simoni</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>109</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Fernanda Anselmo</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>110</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Gabriel Balparda Fasola</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>111</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gabriel de Abreu Burgos Gonçalves</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>112</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Gabriel Marcon Coelho</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>113</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gabriel Silveira da Silva</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>114</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Gabriel Testoni Schmidt</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>115</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Gabriela Hammes</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>116</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gianfranco Longo</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>117</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Giovanna Kiehn Bertuzzi</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>118</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Gladson Hoffmann da Silva</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>119</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Graziella Mendez Cardoso Bridi</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Guilherme Gonçalves</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>121</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Gustavo Husadel Poyer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>122</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Helen Berwanger</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>123</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Higino Ilson da Silva</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>124</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ícaro Rocha de Matos</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>125</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Isabela Warmling Bezerra</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>126</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Isabelle Melo de Souza</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Isabelle Yasmin Trombetta</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Isis Soares Pereira do Nascimento</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jacqueline Alves Ramos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>130</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Jailson Osni Godinho</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>131</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Jean Francesco Arsego</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>132</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>João Lorenço Novaes Pessoa</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>133</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>João Vítor Eccel</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>134</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Julia Rataichesck Fiates</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>135</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Julia Teresa Bruch</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>136</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Juliana Dutra Miranda</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>137</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Karla Albino Cardoso</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>138</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Leonardo Barbosa Pacheco</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>139</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Leonardo Mazzaferro</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>140</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Leticia Silveira Moy</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>141</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Lucas Born Passoni</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>142</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lucas Carvalho Delowski</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>143</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lúcio Costa Proença</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>144</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Marcela Nettuzzi Faorlin</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>145</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Marcel Vechi</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>146</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Marcelo Marcel Cordova</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>147</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Maria Amália Marcon</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>148</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Maria Clara Sampaio Rosa e Silva</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>149</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Maria Paula Silveira</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>150</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mariana Minati de Pinho</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>151</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Marta Elisa Vettori Dalsenter</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>152</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Matheus de Cezaro Menegatti</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>153</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Matheus Rosado Vill</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>154</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Maurício Martini</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>155</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Mirela Moreira Ribeiro</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6997171456515468</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>156</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Natália Castro de Oliveira</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>157</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Natália Mattos da Silva</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>158</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Natália Sens Fedrigo</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>159</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Osman Jose Reyes Alberto</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>160</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Paulo Lucas</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>161</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Paulo Jorge Ramos</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>162</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pauline Cristiane Kammers</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>163</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pedro Augusto Pinho Assi</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>164</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Pedro Schondermark</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>165</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Priscila Mei Minku</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>166</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Rachel Sarreta</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>167</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ramon Felipe Wasch Paes</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>168</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Renato B C Coelho</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>169</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Rafael C de Oliveira</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>170</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ricardo Danilo Rosa</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>171</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Ricardo Massignani</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>172</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Richard Williann Schmidt</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>173</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Roberto Holanda Campelo</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>174</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sulayre Mengotti Oliveira</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>175</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Thaiane Cristina Stahnke Manorov</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>176</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Thiago Belotto</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>177</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Thiago Filippon Xavier</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>178</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Tiago Tamanini Junior</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>179</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Uther Zanin Baldissera</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>180</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Victor Corrêa Canto</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>181</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Vinicius Bubniak</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>182</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Vinicius Marcos Figueiredo</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>183</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Viviane Ciupka</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>184</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Vlademir Senger</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>185</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Yuri Triska</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
         </is>
       </c>
     </row>

--- a/dados_site/membros.xlsx
+++ b/dados_site/membros.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J191"/>
+  <dimension ref="A1:J195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -665,42 +665,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Igor Catão Martins Vaz</t>
+          <t>Aline Schaefer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Doutorando</t>
+          <t>Pós-Doutoranda</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Doutorando</t>
+          <t>Pesquisadora Pós-Doc</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>igorcmvaz.png</t>
+          <t>alineschaefer.png</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>./assets/team/igorcmvaz.png</t>
+          <t>./assets/team/alineschaefer.png</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0003-2433-223X</t>
+          <t>https://orcid.org/0000-0001-8870-9863</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/3846201039408286</t>
+          <t>http://lattes.cnpq.br/8826147751184750</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Igor-Vaz-3</t>
+          <t>https://www.researchgate.net/profile/Aline-Schaefer</t>
         </is>
       </c>
     </row>
@@ -710,42 +710,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aline Schaefer</t>
+          <t>Rafael Almeida Flores</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pós-Doutoranda</t>
+          <t>Pós-Doutorando</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesquisadora Pós-Doc</t>
+          <t>Pesquisador Pós-Doc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>alineschaefer.png</t>
+          <t>rafaelflores.jpeg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>./assets/team/alineschaefer.png</t>
+          <t>./assets/team/rafaelflores.jpeg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0001-8870-9863</t>
+          <t>https://orcid.org/0000-0002-9374-1865</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/8826147751184750</t>
+          <t>https://lattes.cnpq.br/3476347525352024</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Aline-Schaefer</t>
+          <t>https://www.researchgate.net/profile/Rafael-Flores-21?ev=prf_overview</t>
         </is>
       </c>
     </row>
@@ -755,22 +755,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Joelia Silva Cavalcante</t>
+          <t>Igor Catão Martins Vaz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Doutoranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Doutoranda</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>joeliacavalcante@gmail.com</t>
+          <t>Doutorando</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>igorcmvaz.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>./assets/team/igorcmvaz.png</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0003-2433-223X</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/3846201039408286</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Igor-Vaz-3</t>
         </is>
       </c>
     </row>
@@ -780,7 +800,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dilson Machado Cunha</t>
+          <t>Hedelvan Emerson Fardin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -791,6 +811,31 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>Doutorando</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hedelvan.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>./assets/team/hedelvan.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-5838-6733</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/1136405611229993</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Hedelvan-Fardin?ev=hdr_xprf</t>
         </is>
       </c>
     </row>
@@ -800,17 +845,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marco Aurelio Vieira Boufleur</t>
+          <t>Joelia Silva Cavalcante</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Doutorando</t>
+          <t>Doutoranda</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Doutorando</t>
+          <t>Doutoranda</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>joeliacavalcante@gmail.com</t>
         </is>
       </c>
     </row>
@@ -820,42 +870,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Priscila Zampier</t>
+          <t>Dilson Machado Cunha</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mestranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mestranda</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>priscila.jpeg</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>./assets/team/priscila.jpeg</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0001-5577-2441</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://lattes.cnpq.br/2233053067068322</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>https://www.researchgate.net/profile/Priscila-Zampier-2?ev=hdr_xprf</t>
+          <t>Doutorando</t>
         </is>
       </c>
     </row>
@@ -865,22 +890,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amanda Costa Ramos</t>
+          <t>Marco Aurelio Vieira Boufleur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mestranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mestranda</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>amanda.costa.arqeurb@gmail.com</t>
+          <t>Doutorando</t>
         </is>
       </c>
     </row>
@@ -890,17 +910,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Laryssa Bitencourt Anselmo</t>
+          <t>Maurício Tonial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mestranda</t>
+          <t>Doutorando</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mestranda</t>
+          <t>Doutorando</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mauriciotonial.jpeg</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>./assets/team/mauriciotonial.jpeg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-8806-5586</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/2550386614107842</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Mauricio-Tonial</t>
         </is>
       </c>
     </row>
@@ -910,17 +955,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>João Pedro Gemelli Reali</t>
+          <t>Priscila Zampier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mestrando</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mestrando</t>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>priscila.jpeg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>./assets/team/priscila.jpeg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0001-5577-2441</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://lattes.cnpq.br/2233053067068322</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Priscila-Zampier-2?ev=hdr_xprf</t>
         </is>
       </c>
     </row>
@@ -930,42 +1000,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matheus Do Nascimento Martins</t>
+          <t>Amanda Costa Ramos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mestrando</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mestrando</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>matheusmartins.JPG</t>
+          <t>amandaramos.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>./assets/team/matheusmartins.JPG</t>
+          <t>./assets/team/amandaramos.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://orcid.org/0009-0007-5434-8693</t>
+          <t>https://orcid.org/0009-0003-4233-1916</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://lattes.cnpq.br/8801886077639414</t>
+          <t>http://lattes.cnpq.br/7093081804402916</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Matheus-Martins-57</t>
+          <t>https://www.researchgate.net/profile/Amanda-Ramos-33?ev=hdr_xprf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>amanda.costa.arqeurb@gmail.com</t>
         </is>
       </c>
     </row>
@@ -975,7 +1050,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rita Carolina Aimi</t>
+          <t>Laryssa Bitencourt Anselmo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -986,6 +1061,31 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>laryssa.JPG</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>./assets/team/laryssa.JPG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0005-6226-6482</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/1140397275052549</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Laryssa-Bitencourt-Anselmo-2</t>
         </is>
       </c>
     </row>
@@ -995,42 +1095,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rafael Almeida Flores</t>
+          <t>João Pedro Gemelli Reali</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pós-Doutorando</t>
+          <t>Mestrando</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pesquisador Pós-Doc</t>
+          <t>Mestrando</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rafaelflores.jpeg</t>
+          <t>joaoreali.png</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>./assets/team/rafaelflores.jpeg</t>
+          <t>./assets/team/joaoreali.png</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-9374-1865</t>
+          <t>https://orcid.org/0009-0004-2894-3358</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://lattes.cnpq.br/3476347525352024</t>
+          <t>http://lattes.cnpq.br/0417273364484908</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Rafael-Flores-21?ev=prf_overview</t>
+          <t>https://www.researchgate.net/profile/Joao-Pedro-Gemelli-Reali?ev=hdr_xprf</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1140,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Andrea Teston</t>
+          <t>Matheus Do Nascimento Martins</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ex-Membro Pós-Doc</t>
+          <t>Mestrando</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora Pós-Doc</t>
+          <t>Mestrando</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>matheusmartins.JPG</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>./assets/team/matheusmartins.JPG</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0007-5434-8693</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://lattes.cnpq.br/8801886077639414</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Matheus-Martins-57</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1185,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Celimar Azambuja Teixeira</t>
+          <t>Rita Carolina Aimi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ex-Membro Pós-Doc</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora Pós-Doc</t>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ritaaimi.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>./assets/team/ritaaimi.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0006-2002-0529</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/6702681725561460</t>
+          <t>http://lattes.cnpq.br/6906714712146099</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Rita-Aimi?ev=hdr_xprf</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1230,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cláudia Donald Pereira</t>
+          <t>Vitória Vicente Coltri</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ex-Membro Pós-Doc</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora Pós-Doc</t>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vitoriacoltri.jpeg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>./assets/team/vitoriacoltri.jpeg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0001-5724-9208</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/8663301891731042</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Vitoria-Coltri?ev=hdr_xprf</t>
         </is>
       </c>
     </row>
@@ -1105,22 +1275,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ricardo Forgiarini Rupp</t>
+          <t>Mariana Souto dos Anjos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ex-Membro Pós-Doc</t>
+          <t>Mestranda</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador Pós-Doc</t>
+          <t>Mestranda</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>marianaanjos.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>./assets/team/marianaanjos.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/0355666000210770</t>
+          <t>http://lattes.cnpq.br/5374050645646016</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1310,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Taylana Piccinini Scolaro</t>
+          <t>Andrea Teston</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1141,11 +1321,6 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>Ex-Pesquisadora Pós-Doc</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/7183244717269690</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1330,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ana Kelly Marinoski Ribeiro</t>
+          <t>Celimar Azambuja Teixeira</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ex-Membro Doutorado</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6702681725561460</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1355,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Andreza Kalbusch</t>
+          <t>Cláudia Donald Pereira</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ex-Membro Doutorado</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
         </is>
       </c>
     </row>
@@ -1195,22 +1375,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Arthur Santos Silva</t>
+          <t>Ricardo Forgiarini Rupp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ex-Membro Doutorado</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisador Pós-Doc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://lattes.cnpq.br/7017962493418481</t>
+          <t>http://lattes.cnpq.br/0355666000210770</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1400,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bruna Faitão Balvedi</t>
+          <t>Taylana Piccinini Scolaro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ex-Membro Doutorado</t>
+          <t>Ex-Membro Pós-Doc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisadora Pós-Doc</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/7183244717269690</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1425,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bruna Just Meller</t>
+          <t>Ana Kelly Marinoski Ribeiro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1260,7 +1445,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Diego Antônio Custódio</t>
+          <t>Andreza Kalbusch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,7 +1455,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1465,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Igor Schnaider de Souza</t>
+          <t>Arthur Santos Silva</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1291,6 +1476,11 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/7017962493418481</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1490,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Isabel Kroeff Braz</t>
+          <t>Bruna Faitão Balvedi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1320,7 +1510,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lucas Niehuns Antunes</t>
+          <t>Bruna Just Meller</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1330,7 +1520,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1530,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luiz Solon Souza Barreto</t>
+          <t>Diego Antônio Custódio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1360,7 +1550,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marina Ribeiro Viana</t>
+          <t>Igor Schnaider de Souza</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1370,7 +1560,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1570,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mateus Vinícius Bavaresco</t>
+          <t>Isabel Kroeff Braz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1390,12 +1580,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/1682595069602838</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1590,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Matheus Soares Geraldi</t>
+          <t>Lucas Niehuns Antunes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1425,7 +1610,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Talita Flores Dias</t>
+          <t>Luiz Solon Souza Barreto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1435,7 +1620,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1630,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tânia Mara Sebben Oneda</t>
+          <t>Marina Ribeiro Viana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1465,7 +1650,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Thayane Lodete Bilésimo</t>
+          <t>Mateus Vinícius Bavaresco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1475,7 +1660,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/1682595069602838</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1675,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ulisses Munarim</t>
+          <t>Matheus Soares Geraldi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1505,7 +1695,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deivis Luis Marinoski</t>
+          <t>Talita Flores Dias</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1515,12 +1705,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/3425265765339888</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1715,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Andrea Invidiata</t>
+          <t>Tânia Mara Sebben Oneda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1541,11 +1726,6 @@
       <c r="D44" t="inlineStr">
         <is>
           <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/0578767852356933</t>
         </is>
       </c>
     </row>
@@ -1555,22 +1735,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abel Silva Vieira</t>
+          <t>Thayane Lodete Bilésimo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ex-Membro Mestrado</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/6438763922605609</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1755,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aline Eloize Borgert</t>
+          <t>Ulisses Munarim</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ex-Membro Mestrado</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1600,17 +1775,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Andrigo Demetrio da Silva</t>
+          <t>Deivis Luis Marinoski</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ex-Membro Mestrado</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/3425265765339888</t>
         </is>
       </c>
     </row>
@@ -1620,17 +1800,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ariadne Marques de Mendonça</t>
+          <t>Andrea Invidiata</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ex-Membro Mestrado</t>
+          <t>Ex-Membro Doutorado</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/0578767852356933</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1825,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Augusto Martins Marques</t>
+          <t>Abel Silva Vieira</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1651,6 +1836,11 @@
       <c r="D49" t="inlineStr">
         <is>
           <t>Ex-Pesquisador</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6438763922605609</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1850,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cláudia Morishita</t>
+          <t>Aline Eloize Borgert</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1680,7 +1870,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Douglas Ancelmo Freitas</t>
+          <t>Andrigo Demetrio da Silva</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1700,7 +1890,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eduardo Pierozan</t>
+          <t>Ariadne Marques de Mendonça</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1710,7 +1900,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1910,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eldenir Guedes Teodoro</t>
+          <t>Augusto Martins Marques</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1740,7 +1930,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Epaminondas de Souza Lage</t>
+          <t>Cláudia Morishita</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1750,7 +1940,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1950,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fabrícia de Oliveira Grando</t>
+          <t>Douglas Ancelmo Freitas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1770,7 +1960,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1970,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Greici Ramos</t>
+          <t>Eduardo Pierozan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1790,7 +1980,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1990,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gustavo Coutinho Rosa</t>
+          <t>Eldenir Guedes Teodoro</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1820,7 +2010,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jéssica Kuntz Maykot</t>
+          <t>Epaminondas de Souza Lage</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1830,7 +2020,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1840,7 +2030,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Joana Anny Mafalda de Oliveira</t>
+          <t>Fabrícia de Oliveira Grando</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1860,7 +2050,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>José Francisco Campos Moreira</t>
+          <t>Greici Ramos</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1870,7 +2060,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -1880,7 +2070,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Julia Beatriz Saugo Milani</t>
+          <t>Gustavo Coutinho Rosa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1890,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1900,7 +2090,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Juliana May Sangoi</t>
+          <t>Jéssica Kuntz Maykot</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1920,7 +2110,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kácia Henderson Barbosa</t>
+          <t>Joana Anny Mafalda de Oliveira</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1940,7 +2130,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Laiane Susan S. Almeida</t>
+          <t>José Francisco Campos Moreira</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1950,7 +2140,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2150,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lais de Bortoli Klein</t>
+          <t>Julia Beatriz Saugo Milani</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1980,7 +2170,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Laura Michelle Leite Ribeiro</t>
+          <t>Juliana May Sangoi</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2000,7 +2190,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Leticia Dalpaz de Azevedo</t>
+          <t>Kácia Henderson Barbosa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2020,7 +2210,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Luís Fernando Kidinho Araújo dos Santos</t>
+          <t>Laiane Susan S. Almeida</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2030,7 +2220,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2230,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marcelo Dalmédico Ioris</t>
+          <t>Lais de Bortoli Klein</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2050,7 +2240,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2250,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Marina Vasconcelos Santana</t>
+          <t>Laura Michelle Leite Ribeiro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2080,7 +2270,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Marlon Eduardo Rodrigues</t>
+          <t>Leticia Dalpaz de Azevedo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2090,7 +2280,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2290,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mauricio Dias da Conceição Neto</t>
+          <t>Luís Fernando Kidinho Araújo dos Santos</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2120,7 +2310,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Roberta Jacoby Cureau</t>
+          <t>Marcelo Dalmédico Ioris</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2130,7 +2320,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2330,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rodrigo Novais Istchuk</t>
+          <t>Marina Vasconcelos Santana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2150,7 +2340,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2350,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tiago Arent Longo</t>
+          <t>Marlon Eduardo Rodrigues</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2180,7 +2370,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tiago Diehl de Souza</t>
+          <t>Mauricio Dias da Conceição Neto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2200,7 +2390,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vinicius Luis Rocha</t>
+          <t>Roberta Jacoby Cureau</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2210,7 +2400,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador</t>
+          <t>Ex-Pesquisadora</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2410,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wagner Isidoro Simioni</t>
+          <t>Rodrigo Novais Istchuk</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2240,7 +2430,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Max Weeber</t>
+          <t>Tiago Arent Longo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2260,17 +2450,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acácio Gomes Corrêa Silvestre</t>
+          <t>Tiago Diehl de Souza</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ex-Membro Graduação</t>
+          <t>Ex-Membro Mestrado</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador(a)</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -2280,17 +2470,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alef Pereira</t>
+          <t>Vinicius Luis Rocha</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ex-Membro Graduação</t>
+          <t>Ex-Membro Mestrado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador(a)</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -2300,17 +2490,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alexandre Maestri</t>
+          <t>Wagner Isidoro Simioni</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ex-Membro Graduação</t>
+          <t>Ex-Membro Mestrado</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador(a)</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -2320,17 +2510,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amanda Geraldo Andrighi</t>
+          <t>Max Weeber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ex-Membro Graduação</t>
+          <t>Ex-Membro Mestrado</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador(a)</t>
+          <t>Ex-Pesquisador</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2530,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ana Gabriela S A Cardoso</t>
+          <t>Acácio Gomes Corrêa Silvestre</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2360,7 +2550,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ana Júlia Deffaci Deresz</t>
+          <t>Alef Pereira</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2380,7 +2570,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ana Júlia Heisler de Oliveira</t>
+          <t>Alexandre Maestri</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2400,7 +2590,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>André Castellani Lopes</t>
+          <t>Amanda Geraldo Andrighi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2420,7 +2610,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>André Neis Botelho</t>
+          <t>Ana Gabriela S A Cardoso</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2440,7 +2630,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Andreza Montibeller</t>
+          <t>Ana Júlia Deffaci Deresz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2460,7 +2650,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Anna Luiza Schiefler Wallner</t>
+          <t>Ana Júlia Heisler de Oliveira</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2480,7 +2670,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Anthony Midori Fugi</t>
+          <t>André Castellani Lopes</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2500,7 +2690,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Beatriz Bayestorff Muller</t>
+          <t>André Neis Botelho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2520,7 +2710,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bernardo Farias Asmus</t>
+          <t>Andreza Montibeller</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2540,7 +2730,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bruno Ariosa de Souza</t>
+          <t>Anna Luiza Schiefler Wallner</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2560,7 +2750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Caio Morelli Figueroba</t>
+          <t>Anthony Midori Fugi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2580,7 +2770,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Caio Wolf Klein</t>
+          <t>Beatriz Bayestorff Muller</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2600,7 +2790,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Candi Citadini de Oliveira</t>
+          <t>Bernardo Farias Asmus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2620,7 +2810,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Carolina Cannella Peña</t>
+          <t>Bruno Ariosa de Souza</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2640,7 +2830,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cecília Soares Faco</t>
+          <t>Caio Morelli Figueroba</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2660,7 +2850,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Daniel Fabricio Ferreira</t>
+          <t>Caio Wolf Klein</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2680,7 +2870,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dario Menegasso Pires</t>
+          <t>Candi Citadini de Oliveira</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2700,7 +2890,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Davi da Fonseca Tavares</t>
+          <t>Carolina Cannella Peña</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2720,7 +2910,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>David Junior Gonçalves da Silva</t>
+          <t>Cecília Soares Faco</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2740,7 +2930,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Débora Casasola</t>
+          <t>Daniel Fabricio Ferreira</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2760,7 +2950,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Diego Bressan</t>
+          <t>Dario Menegasso Pires</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2780,7 +2970,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Douglas Gherardt Brecht</t>
+          <t>Davi da Fonseca Tavares</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2800,7 +2990,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Douglas Leandro Meincheim</t>
+          <t>David Junior Gonçalves da Silva</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2820,7 +3010,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Douglas Vigarani Scalco</t>
+          <t>Débora Casasola</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2840,7 +3030,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Eduardo Bald</t>
+          <t>Diego Bressan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2860,7 +3050,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eduardo Leite Souza</t>
+          <t>Douglas Gherardt Brecht</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2880,7 +3070,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Eric Serafim Franco</t>
+          <t>Douglas Leandro Meincheim</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2900,7 +3090,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Felipe Cidade Soares</t>
+          <t>Douglas Vigarani Scalco</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2920,7 +3110,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Felipe Martini</t>
+          <t>Eduardo Bald</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2940,7 +3130,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Felipe Scotti Alves Tonin Simoni</t>
+          <t>Eduardo Leite Souza</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2960,7 +3150,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fernanda Anselmo</t>
+          <t>Eric Serafim Franco</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2980,7 +3170,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gabriel Balparda Fasola</t>
+          <t>Felipe Cidade Soares</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3000,7 +3190,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Gabriel de Abreu Burgos Gonçalves</t>
+          <t>Felipe Martini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3020,7 +3210,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Gabriel Marcon Coelho</t>
+          <t>Felipe Scotti Alves Tonin Simoni</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3040,7 +3230,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Gabriel Silveira da Silva</t>
+          <t>Fernanda Anselmo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3060,7 +3250,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Gabriel Testoni Schmidt</t>
+          <t>Gabriel Balparda Fasola</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3080,7 +3270,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Gabriela Hammes</t>
+          <t>Gabriel de Abreu Burgos Gonçalves</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3100,7 +3290,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gianfranco Longo</t>
+          <t>Gabriel Marcon Coelho</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3120,7 +3310,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Giovanna Kiehn Bertuzzi</t>
+          <t>Gabriel Silveira da Silva</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3140,7 +3330,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Gladson Hoffmann da Silva</t>
+          <t>Gabriel Testoni Schmidt</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3160,7 +3350,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Graziella Mendez Cardoso Bridi</t>
+          <t>Gabriela Hammes</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3180,7 +3370,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guilherme Gonçalves</t>
+          <t>Gianfranco Longo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3200,7 +3390,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gustavo Husadel Poyer</t>
+          <t>Giovanna Kiehn Bertuzzi</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3220,7 +3410,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Helen Berwanger</t>
+          <t>Gladson Hoffmann da Silva</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3240,7 +3430,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Higino Ilson da Silva</t>
+          <t>Graziella Mendez Cardoso Bridi</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3260,7 +3450,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ícaro Rocha de Matos</t>
+          <t>Guilherme Gonçalves</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3280,7 +3470,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Isabela Warmling Bezerra</t>
+          <t>Gustavo Husadel Poyer</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3300,7 +3490,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Isabelle Melo de Souza</t>
+          <t>Helen Berwanger</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3320,7 +3510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Isabelle Yasmin Trombetta</t>
+          <t>Higino Ilson da Silva</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3340,7 +3530,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Isis Soares Pereira do Nascimento</t>
+          <t>Ícaro Rocha de Matos</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,7 +3550,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jacqueline Alves Ramos</t>
+          <t>Isabela Warmling Bezerra</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3380,7 +3570,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jailson Osni Godinho</t>
+          <t>Isabelle Melo de Souza</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3400,7 +3590,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jean Francesco Arsego</t>
+          <t>Isabelle Yasmin Trombetta</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3420,7 +3610,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>João Lorenço Novaes Pessoa</t>
+          <t>Isis Soares Pereira do Nascimento</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3440,7 +3630,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>João Vítor Eccel</t>
+          <t>Jacqueline Alves Ramos</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3460,7 +3650,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Julia Rataichesck Fiates</t>
+          <t>Jailson Osni Godinho</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3480,7 +3670,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Julia Teresa Bruch</t>
+          <t>Jean Francesco Arsego</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3500,7 +3690,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Juliana Dutra Miranda</t>
+          <t>João Lorenço Novaes Pessoa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3520,7 +3710,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Karla Albino Cardoso</t>
+          <t>João Vítor Eccel</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3540,7 +3730,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Leonardo Barbosa Pacheco</t>
+          <t>Julia Rataichesck Fiates</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3560,7 +3750,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Leonardo Mazzaferro</t>
+          <t>Julia Teresa Bruch</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3580,7 +3770,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Leticia Silveira Moy</t>
+          <t>Juliana Dutra Miranda</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3600,7 +3790,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lucas Born Passoni</t>
+          <t>Karla Albino Cardoso</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3620,7 +3810,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lucas Carvalho Delowski</t>
+          <t>Leonardo Barbosa Pacheco</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3640,7 +3830,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lúcio Costa Proença</t>
+          <t>Leonardo Mazzaferro</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3660,7 +3850,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Marcela Nettuzzi Faorlin</t>
+          <t>Leticia Silveira Moy</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3680,7 +3870,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Marcel Vechi</t>
+          <t>Lucas Born Passoni</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3700,7 +3890,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Marcelo Marcel Cordova</t>
+          <t>Lucas Carvalho Delowski</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3720,7 +3910,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Maria Amália Marcon</t>
+          <t>Lúcio Costa Proença</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3740,7 +3930,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Maria Clara Sampaio Rosa e Silva</t>
+          <t>Marcela Nettuzzi Faorlin</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3760,7 +3950,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Maria Paula Silveira</t>
+          <t>Marcel Vechi</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3780,7 +3970,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mariana Minati de Pinho</t>
+          <t>Marcelo Marcel Cordova</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3800,7 +3990,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Marta Elisa Vettori Dalsenter</t>
+          <t>Maria Amália Marcon</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3820,7 +4010,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Matheus de Cezaro Menegatti</t>
+          <t>Maria Clara Sampaio Rosa e Silva</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3840,7 +4030,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Matheus Rosado Vill</t>
+          <t>Maria Paula Silveira</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3860,7 +4050,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Maurício Martini</t>
+          <t>Mariana Minati de Pinho</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3880,7 +4070,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mirela Moreira Ribeiro</t>
+          <t>Marta Elisa Vettori Dalsenter</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3890,12 +4080,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ex-Pesquisadora</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>http://lattes.cnpq.br/6997171456515468</t>
+          <t>Ex-Pesquisador(a)</t>
         </is>
       </c>
     </row>
@@ -3905,7 +4090,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Natália Castro de Oliveira</t>
+          <t>Matheus de Cezaro Menegatti</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3925,7 +4110,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Natália Mattos da Silva</t>
+          <t>Matheus Rosado Vill</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3945,7 +4130,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Natália Sens Fedrigo</t>
+          <t>Maurício Martini</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3965,7 +4150,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Osman Jose Reyes Alberto</t>
+          <t>Mirela Moreira Ribeiro</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3975,7 +4160,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Ex-Pesquisador(a)</t>
+          <t>Ex-Pesquisadora</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>http://lattes.cnpq.br/6997171456515468</t>
         </is>
       </c>
     </row>
@@ -3985,7 +4175,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Paulo Lucas</t>
+          <t>Natália Castro de Oliveira</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4005,7 +4195,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Paulo Jorge Ramos</t>
+          <t>Natália Mattos da Silva</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4025,7 +4215,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pauline Cristiane Kammers</t>
+          <t>Natália Sens Fedrigo</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4045,7 +4235,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Pedro Augusto Pinho Assi</t>
+          <t>Osman Jose Reyes Alberto</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4065,7 +4255,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pedro Schondermark</t>
+          <t>Paulo Lucas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4085,7 +4275,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Priscila Mei Minku</t>
+          <t>Paulo Jorge Ramos</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4105,7 +4295,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Rachel Sarreta</t>
+          <t>Pauline Cristiane Kammers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4125,7 +4315,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ramon Felipe Wasch Paes</t>
+          <t>Pedro Augusto Pinho Assi</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4145,7 +4335,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Renato B C Coelho</t>
+          <t>Pedro Schondermark</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4165,7 +4355,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Rafael C de Oliveira</t>
+          <t>Priscila Mei Minku</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4185,7 +4375,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ricardo Danilo Rosa</t>
+          <t>Rachel Sarreta</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4205,7 +4395,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ricardo Massignani</t>
+          <t>Ramon Felipe Wasch Paes</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4225,7 +4415,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Richard Williann Schmidt</t>
+          <t>Renato B C Coelho</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4245,7 +4435,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Roberto Holanda Campelo</t>
+          <t>Rafael C de Oliveira</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4265,7 +4455,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sulayre Mengotti Oliveira</t>
+          <t>Ricardo Danilo Rosa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4285,7 +4475,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Thaiane Cristina Stahnke Manorov</t>
+          <t>Ricardo Massignani</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4305,7 +4495,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Thiago Belotto</t>
+          <t>Richard Williann Schmidt</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4325,7 +4515,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Thiago Filippon Xavier</t>
+          <t>Roberto Holanda Campelo</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4345,7 +4535,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tiago Tamanini Junior</t>
+          <t>Sulayre Mengotti Oliveira</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4365,7 +4555,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Uther Zanin Baldissera</t>
+          <t>Thaiane Cristina Stahnke Manorov</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4385,7 +4575,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Victor Corrêa Canto</t>
+          <t>Thiago Belotto</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4405,7 +4595,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Vinicius Bubniak</t>
+          <t>Thiago Filippon Xavier</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4425,7 +4615,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Vinicius Marcos Figueiredo</t>
+          <t>Tiago Tamanini Junior</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4445,7 +4635,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Viviane Ciupka</t>
+          <t>Uther Zanin Baldissera</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4465,7 +4655,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Vlademir Senger</t>
+          <t>Victor Corrêa Canto</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4485,15 +4675,95 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>Vinicius Bubniak</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>186</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Vinicius Marcos Figueiredo</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>187</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Viviane Ciupka</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>188</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Vlademir Senger</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ex-Pesquisador(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>189</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>Yuri Triska</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Ex-Membro Graduação</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ex-Membro Graduação</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
         <is>
           <t>Ex-Pesquisador(a)</t>
         </is>
